--- a/database/event/3392/event_3392_evp_summary.xlsx
+++ b/database/event/3392/event_3392_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.2605</v>
+        <v>11.2237</v>
       </c>
       <c r="C2" t="n">
-        <v>6.0211</v>
+        <v>6.0014</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1276</v>
+        <v>4.0276</v>
       </c>
       <c r="E2" t="n">
-        <v>11.2605</v>
+        <v>11.2237</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7751</v>
+        <v>4.7382</v>
       </c>
       <c r="G2" t="n">
         <v>6.4855</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1843</v>
+        <v>5.1265</v>
       </c>
       <c r="I2" t="n">
         <v>5.257</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.1178</v>
+        <v>11.0839</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9447</v>
+        <v>5.9266</v>
       </c>
       <c r="D3" t="n">
-        <v>4.07</v>
+        <v>3.9719</v>
       </c>
       <c r="E3" t="n">
-        <v>11.1178</v>
+        <v>11.0839</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5086</v>
+        <v>4.4747</v>
       </c>
       <c r="G3" t="n">
         <v>6.6092</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7664</v>
+        <v>4.7132</v>
       </c>
       <c r="I3" t="n">
         <v>4.8332</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.3909</v>
+        <v>7.939</v>
       </c>
       <c r="C4" t="n">
-        <v>3.952</v>
+        <v>4.245</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5644</v>
+        <v>2.719</v>
       </c>
       <c r="E4" t="n">
-        <v>7.3909</v>
+        <v>7.939</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5718</v>
+        <v>3.12</v>
       </c>
       <c r="G4" t="n">
         <v>4.819</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5718</v>
+        <v>3.12</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5958</v>
+        <v>3.1727</v>
       </c>
       <c r="J4" t="n">
         <v>4.819</v>
@@ -621,7 +621,7 @@
         <v>243</v>
       </c>
       <c r="M4" t="n">
-        <v>7.4148</v>
+        <v>7.9917</v>
       </c>
       <c r="N4" t="n">
         <v>497</v>
@@ -630,81 +630,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1574</v>
+        <v>5.3464</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7577</v>
+        <v>2.8587</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6621</v>
+        <v>1.6861</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1574</v>
+        <v>5.3464</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2169</v>
+        <v>4.2055</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9405</v>
+        <v>1.1409</v>
       </c>
       <c r="H5" t="n">
-        <v>4.405</v>
+        <v>4.3594</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5704</v>
+        <v>3.5334</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9405</v>
+        <v>1.1409</v>
       </c>
       <c r="K5" t="n">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="L5" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="M5" t="n">
-        <v>4.510899999999999</v>
+        <v>4.6743</v>
       </c>
       <c r="N5" t="n">
-        <v>201</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0442</v>
+        <v>5.1834</v>
       </c>
       <c r="C6" t="n">
-        <v>2.6972</v>
+        <v>2.7716</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6164</v>
+        <v>1.6212</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0442</v>
+        <v>5.1834</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3041</v>
+        <v>4.2429</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7401</v>
+        <v>0.9405</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7559</v>
+        <v>4.5099</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8548</v>
+        <v>3.6554</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7401</v>
+        <v>0.9405</v>
       </c>
       <c r="K6" t="n">
         <v>121</v>
@@ -713,7 +713,7 @@
         <v>80</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5949</v>
+        <v>4.5959</v>
       </c>
       <c r="N6" t="n">
         <v>201</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.0327</v>
+        <v>5.1121</v>
       </c>
       <c r="C7" t="n">
-        <v>2.691</v>
+        <v>2.7335</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6117</v>
+        <v>1.5928</v>
       </c>
       <c r="E7" t="n">
-        <v>5.0327</v>
+        <v>5.1121</v>
       </c>
       <c r="F7" t="n">
-        <v>1.699</v>
+        <v>4.372</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3337</v>
+        <v>0.7401</v>
       </c>
       <c r="H7" t="n">
-        <v>1.699</v>
+        <v>5.029</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7149</v>
+        <v>4.0761</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3337</v>
+        <v>0.7401</v>
       </c>
       <c r="K7" t="n">
-        <v>254</v>
+        <v>121</v>
       </c>
       <c r="L7" t="n">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="M7" t="n">
-        <v>5.0486</v>
+        <v>4.8162</v>
       </c>
       <c r="N7" t="n">
-        <v>497</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.9351</v>
+        <v>5.0201</v>
       </c>
       <c r="C8" t="n">
-        <v>2.6388</v>
+        <v>2.6843</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5723</v>
+        <v>1.5561</v>
       </c>
       <c r="E8" t="n">
-        <v>4.9351</v>
+        <v>5.0201</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7942</v>
+        <v>1.6864</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1409</v>
+        <v>3.3337</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7942</v>
+        <v>1.6864</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0753</v>
+        <v>1.7149</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1409</v>
+        <v>3.3337</v>
       </c>
       <c r="K8" t="n">
-        <v>142</v>
+        <v>254</v>
       </c>
       <c r="L8" t="n">
-        <v>87</v>
+        <v>243</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2162</v>
+        <v>5.0486</v>
       </c>
       <c r="N8" t="n">
-        <v>229</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.6837</v>
+        <v>4.8179</v>
       </c>
       <c r="C9" t="n">
-        <v>2.5044</v>
+        <v>2.5762</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4707</v>
+        <v>1.4755</v>
       </c>
       <c r="E9" t="n">
-        <v>4.6837</v>
+        <v>4.8179</v>
       </c>
       <c r="F9" t="n">
-        <v>4.7068</v>
+        <v>4.841</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0231</v>
       </c>
       <c r="H9" t="n">
-        <v>6.3761</v>
+        <v>6.9161</v>
       </c>
       <c r="I9" t="n">
-        <v>5.168</v>
+        <v>5.6057</v>
       </c>
       <c r="J9" t="n">
         <v>-0.0231</v>
@@ -851,7 +851,7 @@
         <v>87</v>
       </c>
       <c r="M9" t="n">
-        <v>5.1449</v>
+        <v>5.582599999999999</v>
       </c>
       <c r="N9" t="n">
         <v>229</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.5314</v>
+        <v>4.6294</v>
       </c>
       <c r="C10" t="n">
-        <v>2.423</v>
+        <v>2.4754</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4092</v>
+        <v>1.4004</v>
       </c>
       <c r="E10" t="n">
-        <v>4.5314</v>
+        <v>4.6294</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2903</v>
+        <v>4.3883</v>
       </c>
       <c r="G10" t="n">
         <v>0.2411</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7003</v>
+        <v>5.0947</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8097</v>
+        <v>4.1294</v>
       </c>
       <c r="J10" t="n">
         <v>0.2411</v>
@@ -897,7 +897,7 @@
         <v>80</v>
       </c>
       <c r="M10" t="n">
-        <v>4.0508</v>
+        <v>4.370500000000001</v>
       </c>
       <c r="N10" t="n">
         <v>201</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.2109</v>
+        <v>4.1905</v>
       </c>
       <c r="C11" t="n">
-        <v>2.2516</v>
+        <v>2.2407</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2797</v>
+        <v>1.2256</v>
       </c>
       <c r="E11" t="n">
-        <v>4.2109</v>
+        <v>4.1905</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2109</v>
+        <v>4.1905</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2996</v>
+        <v>4.2676</v>
       </c>
       <c r="I11" t="n">
         <v>4.3398</v>
@@ -962,7 +962,7 @@
         <v>1.889</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0058</v>
+        <v>0.9636</v>
       </c>
       <c r="E12" t="n">
         <v>3.5328</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.501</v>
+        <v>3.4936</v>
       </c>
       <c r="C13" t="n">
-        <v>1.872</v>
+        <v>1.868</v>
       </c>
       <c r="D13" t="n">
-        <v>0.993</v>
+        <v>0.9479</v>
       </c>
       <c r="E13" t="n">
-        <v>3.501</v>
+        <v>3.4936</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6695</v>
+        <v>0.662</v>
       </c>
       <c r="G13" t="n">
         <v>2.8315</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6695</v>
+        <v>0.662</v>
       </c>
       <c r="I13" t="n">
         <v>0.6788999999999999</v>
@@ -1044,124 +1044,124 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2066</v>
+        <v>3.3788</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7146</v>
+        <v>1.8067</v>
       </c>
       <c r="D14" t="n">
-        <v>0.874</v>
+        <v>0.9022</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2066</v>
+        <v>3.3788</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8928</v>
+        <v>3.3788</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6862</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8928</v>
+        <v>3.3788</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1552</v>
+        <v>3.4072</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6862</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>142</v>
+        <v>257</v>
       </c>
       <c r="L14" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.469</v>
+        <v>3.4072</v>
       </c>
       <c r="N14" t="n">
-        <v>229</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.1511</v>
+        <v>3.2066</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6849</v>
+        <v>1.7146</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8516</v>
+        <v>0.8336</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1511</v>
+        <v>3.2066</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1511</v>
+        <v>3.8928</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.6862</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1511</v>
+        <v>3.8928</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1657</v>
+        <v>3.1552</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.6862</v>
       </c>
       <c r="K15" t="n">
-        <v>257</v>
+        <v>142</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1657</v>
+        <v>2.469</v>
       </c>
       <c r="N15" t="n">
-        <v>257</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.0773</v>
+        <v>3.1402</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6454</v>
+        <v>1.6791</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8218</v>
+        <v>0.8071</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0773</v>
+        <v>3.1402</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0773</v>
+        <v>3.1402</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0773</v>
+        <v>3.1402</v>
       </c>
       <c r="I16" t="n">
-        <v>3.0916</v>
+        <v>3.1666</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0916</v>
+        <v>3.1666</v>
       </c>
       <c r="N16" t="n">
         <v>257</v>
@@ -1192,7 +1192,7 @@
         <v>1.1818</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4715</v>
+        <v>0.4366</v>
       </c>
       <c r="E17" t="n">
         <v>2.2102</v>
@@ -1238,7 +1238,7 @@
         <v>1.1452</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4438</v>
+        <v>0.4093</v>
       </c>
       <c r="E18" t="n">
         <v>2.1417</v>
@@ -1274,139 +1274,139 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.052</v>
+        <v>2.0527</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0972</v>
+        <v>1.0976</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4076</v>
+        <v>0.3739</v>
       </c>
       <c r="E19" t="n">
-        <v>2.052</v>
+        <v>2.0527</v>
       </c>
       <c r="F19" t="n">
-        <v>3.052</v>
+        <v>2.3119</v>
       </c>
       <c r="G19" t="n">
-        <v>-1</v>
+        <v>-0.2592</v>
       </c>
       <c r="H19" t="n">
-        <v>3.052</v>
+        <v>2.3119</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4737</v>
+        <v>2.3313</v>
       </c>
       <c r="J19" t="n">
-        <v>-1</v>
+        <v>-0.2592</v>
       </c>
       <c r="K19" t="n">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="L19" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4737</v>
+        <v>2.0721</v>
       </c>
       <c r="N19" t="n">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0224</v>
+        <v>2.052</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0814</v>
+        <v>1.0972</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3956</v>
+        <v>0.3736</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0224</v>
+        <v>2.052</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0224</v>
+        <v>3.052</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0224</v>
+        <v>3.052</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0413</v>
+        <v>2.4737</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K20" t="n">
-        <v>208</v>
+        <v>121</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0413</v>
+        <v>1.4737</v>
       </c>
       <c r="N20" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0021</v>
+        <v>2.0074</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0705</v>
+        <v>1.0734</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3874</v>
+        <v>0.3558</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0021</v>
+        <v>2.0074</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2613</v>
+        <v>2.0074</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2592</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2613</v>
+        <v>2.0074</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2718</v>
+        <v>2.0413</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2592</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0126</v>
+        <v>2.0413</v>
       </c>
       <c r="N21" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22">
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9289</v>
+        <v>1.9205</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0314</v>
+        <v>1.0269</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3579</v>
+        <v>0.3212</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9289</v>
+        <v>1.9205</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1255</v>
+        <v>1.1171</v>
       </c>
       <c r="G22" t="n">
         <v>0.8034</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1255</v>
+        <v>1.1171</v>
       </c>
       <c r="I22" t="n">
         <v>1.136</v>
@@ -1458,231 +1458,231 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.6606</v>
+        <v>1.7143</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8879</v>
+        <v>0.9166</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2495</v>
+        <v>0.2391</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6606</v>
+        <v>1.7143</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6606</v>
+        <v>1.8653</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.151</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6606</v>
+        <v>1.8653</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6606</v>
+        <v>1.881</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.151</v>
       </c>
       <c r="K23" t="n">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M23" t="n">
-        <v>1.6606</v>
+        <v>1.73</v>
       </c>
       <c r="N23" t="n">
-        <v>169</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.413</v>
+        <v>1.6606</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.8879</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1495</v>
+        <v>0.2177</v>
       </c>
       <c r="E24" t="n">
-        <v>1.413</v>
+        <v>1.6606</v>
       </c>
       <c r="F24" t="n">
-        <v>1.564</v>
+        <v>1.6606</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.151</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.564</v>
+        <v>1.6606</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5712</v>
+        <v>1.6606</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.151</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="L24" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4202</v>
+        <v>1.6606</v>
       </c>
       <c r="N24" t="n">
-        <v>194</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3463</v>
+        <v>1.4887</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7199</v>
+        <v>0.796</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1225</v>
+        <v>0.1492</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3463</v>
+        <v>1.4887</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3463</v>
+        <v>1.4887</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3463</v>
+        <v>1.4887</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3463</v>
+        <v>1.4887</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3463</v>
+        <v>1.4887</v>
       </c>
       <c r="N25" t="n">
-        <v>169</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3356</v>
+        <v>1.3842</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.7401</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1182</v>
+        <v>0.1076</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3356</v>
+        <v>1.3842</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.5762</v>
+        <v>1.3842</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9118</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.5762</v>
+        <v>1.3842</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.5909</v>
+        <v>1.3842</v>
       </c>
       <c r="J26" t="n">
-        <v>2.9118</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>254</v>
+        <v>169</v>
       </c>
       <c r="L26" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3209</v>
+        <v>1.3842</v>
       </c>
       <c r="N26" t="n">
-        <v>497</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1724</v>
+        <v>1.3473</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6269</v>
+        <v>0.7204</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0523</v>
+        <v>0.0929</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1724</v>
+        <v>1.3473</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1724</v>
+        <v>-1.5645</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2.9118</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1724</v>
+        <v>-1.5645</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1724</v>
+        <v>-1.5909</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2.9118</v>
       </c>
       <c r="K27" t="n">
-        <v>169</v>
+        <v>254</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1724</v>
+        <v>1.3209</v>
       </c>
       <c r="N27" t="n">
-        <v>169</v>
+        <v>497</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1313</v>
+        <v>1.2705</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6049</v>
+        <v>0.6793</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0357</v>
+        <v>0.0623</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1313</v>
+        <v>1.2705</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1313</v>
+        <v>1.2705</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1313</v>
+        <v>1.2705</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1313</v>
+        <v>1.2705</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1313</v>
+        <v>1.2705</v>
       </c>
       <c r="N28" t="n">
         <v>122</v>
@@ -1734,415 +1734,415 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cromen</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.0803</v>
+        <v>1.2507</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5776</v>
+        <v>0.6688</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0151</v>
+        <v>0.0544</v>
       </c>
       <c r="E29" t="n">
-        <v>1.0803</v>
+        <v>1.2507</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5958</v>
+        <v>1.2507</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5155</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5958</v>
+        <v>1.2507</v>
       </c>
       <c r="I29" t="n">
-        <v>1.2935</v>
+        <v>1.2507</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5155</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="L29" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7780000000000001</v>
+        <v>1.2507</v>
       </c>
       <c r="N29" t="n">
-        <v>229</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0497</v>
+        <v>1.1724</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5613</v>
+        <v>0.6269</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0027</v>
+        <v>0.0232</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0497</v>
+        <v>1.1724</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0497</v>
+        <v>1.1724</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0497</v>
+        <v>1.1724</v>
       </c>
       <c r="I30" t="n">
-        <v>1.0497</v>
+        <v>1.1724</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.0497</v>
+        <v>1.1724</v>
       </c>
       <c r="N30" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>cromen</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.0258</v>
+        <v>1.0803</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5485</v>
+        <v>0.5776</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.007</v>
+        <v>-0.0135</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0258</v>
+        <v>1.0803</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0258</v>
+        <v>1.5958</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.5155</v>
       </c>
       <c r="H31" t="n">
-        <v>1.0258</v>
+        <v>1.5958</v>
       </c>
       <c r="I31" t="n">
-        <v>1.0306</v>
+        <v>1.2935</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.5155</v>
       </c>
       <c r="K31" t="n">
-        <v>257</v>
+        <v>142</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M31" t="n">
-        <v>1.0306</v>
+        <v>0.7780000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>257</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9311</v>
+        <v>1.0497</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4979</v>
+        <v>0.5613</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0452</v>
+        <v>-0.0257</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9311</v>
+        <v>1.0497</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9311</v>
+        <v>1.0497</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9311</v>
+        <v>1.0497</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9311</v>
+        <v>1.0497</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9311</v>
+        <v>1.0497</v>
       </c>
       <c r="N32" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8588</v>
+        <v>1.035</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4592</v>
+        <v>0.5534</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0316</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8588</v>
+        <v>1.035</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8588</v>
+        <v>1.035</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8588</v>
+        <v>1.035</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8588</v>
+        <v>1.035</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8588</v>
+        <v>1.035</v>
       </c>
       <c r="N33" t="n">
-        <v>169</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8296</v>
+        <v>1.022</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4436</v>
+        <v>0.5465</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0862</v>
+        <v>-0.0367</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8296</v>
+        <v>1.022</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8296</v>
+        <v>1.022</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8296</v>
+        <v>1.022</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8373</v>
+        <v>1.0306</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>208</v>
+        <v>257</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8373</v>
+        <v>1.0306</v>
       </c>
       <c r="N34" t="n">
-        <v>208</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7367</v>
+        <v>0.8234</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3939</v>
+        <v>0.4403</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1238</v>
+        <v>-0.1159</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7367</v>
+        <v>0.8234</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7367</v>
+        <v>0.8234</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7367</v>
+        <v>0.8234</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7367</v>
+        <v>0.8373</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7367</v>
+        <v>0.8373</v>
       </c>
       <c r="N35" t="n">
-        <v>169</v>
+        <v>208</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6824</v>
+        <v>0.7367</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3649</v>
+        <v>0.3939</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1457</v>
+        <v>-0.1504</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6824</v>
+        <v>0.7367</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6824</v>
+        <v>0.7367</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6824</v>
+        <v>0.7367</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6887</v>
+        <v>0.7367</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6887</v>
+        <v>0.7367</v>
       </c>
       <c r="N36" t="n">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5942</v>
+        <v>0.6773</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3177</v>
+        <v>0.3622</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1813</v>
+        <v>-0.1741</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5942</v>
+        <v>0.6773</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5942</v>
+        <v>0.6773</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5942</v>
+        <v>0.6773</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5942</v>
+        <v>0.6887</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5942</v>
+        <v>0.6887</v>
       </c>
       <c r="N37" t="n">
-        <v>122</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.528</v>
+        <v>0.5477</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2823</v>
+        <v>0.2929</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2081</v>
+        <v>-0.2257</v>
       </c>
       <c r="E38" t="n">
-        <v>0.528</v>
+        <v>0.5477</v>
       </c>
       <c r="F38" t="n">
-        <v>0.528</v>
+        <v>0.5477</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.528</v>
+        <v>0.5477</v>
       </c>
       <c r="I38" t="n">
-        <v>0.528</v>
+        <v>0.5477</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.528</v>
+        <v>0.5477</v>
       </c>
       <c r="N38" t="n">
         <v>122</v>
@@ -2204,7 +2204,7 @@
         <v>0.2196</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2555</v>
+        <v>-0.2803</v>
       </c>
       <c r="E39" t="n">
         <v>0.4106</v>
@@ -2250,7 +2250,7 @@
         <v>0.1852</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2815</v>
+        <v>-0.3059</v>
       </c>
       <c r="E40" t="n">
         <v>0.3463</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3144</v>
+        <v>0.3133</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1681</v>
+        <v>0.1675</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2944</v>
+        <v>-0.3191</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3144</v>
+        <v>0.3133</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3144</v>
+        <v>0.3133</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3144</v>
+        <v>0.3133</v>
       </c>
       <c r="I41" t="n">
         <v>0.3159</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2834</v>
+        <v>0.2823</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1515</v>
+        <v>0.1509</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3069</v>
+        <v>-0.3314</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2834</v>
+        <v>0.2823</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2834</v>
+        <v>0.2823</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2834</v>
+        <v>0.2823</v>
       </c>
       <c r="I42" t="n">
         <v>0.2847</v>
@@ -2388,7 +2388,7 @@
         <v>0.1035</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3432</v>
+        <v>-0.3668</v>
       </c>
       <c r="E43" t="n">
         <v>0.1935</v>
@@ -2434,7 +2434,7 @@
         <v>0.0702</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3684</v>
+        <v>-0.3916</v>
       </c>
       <c r="E44" t="n">
         <v>0.1312</v>
@@ -2480,7 +2480,7 @@
         <v>0.0611</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3752</v>
+        <v>-0.3984</v>
       </c>
       <c r="E45" t="n">
         <v>0.1142</v>
@@ -2516,35 +2516,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.0959</v>
+        <v>-0.0725</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0513</v>
+        <v>-0.0388</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4601</v>
+        <v>-0.4728</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0959</v>
+        <v>-0.0725</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7487</v>
+        <v>0.1066</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.8446</v>
+        <v>-0.1791</v>
       </c>
       <c r="H46" t="n">
-        <v>0.7487</v>
+        <v>0.1066</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7487</v>
+        <v>0.1066</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.8446</v>
+        <v>-0.1791</v>
       </c>
       <c r="K46" t="n">
         <v>166</v>
@@ -2553,7 +2553,7 @@
         <v>53</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.09589999999999999</v>
+        <v>-0.07250000000000001</v>
       </c>
       <c r="N46" t="n">
         <v>219</v>
@@ -2562,93 +2562,93 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.1022</v>
+        <v>-0.0959</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0546</v>
+        <v>-0.0513</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4626</v>
+        <v>-0.4821</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.1022</v>
+        <v>-0.0959</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1022</v>
+        <v>0.7487</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-0.8446</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.1022</v>
+        <v>0.7487</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.1022</v>
+        <v>0.7487</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>-0.8446</v>
       </c>
       <c r="K47" t="n">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.1022</v>
+        <v>-0.09589999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>85</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.107</v>
+        <v>-0.1022</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0572</v>
+        <v>-0.0546</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4646</v>
+        <v>-0.4846</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.107</v>
+        <v>-0.1022</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0721</v>
+        <v>-0.1022</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.1791</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0721</v>
+        <v>-0.1022</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0721</v>
+        <v>-0.1022</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.1791</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="L48" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.107</v>
+        <v>-0.1022</v>
       </c>
       <c r="N48" t="n">
-        <v>219</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49">
@@ -2664,7 +2664,7 @@
         <v>-0.1517</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.536</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="E49" t="n">
         <v>-0.2838</v>
@@ -2710,7 +2710,7 @@
         <v>-0.1733</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5523</v>
+        <v>-0.573</v>
       </c>
       <c r="E50" t="n">
         <v>-0.3241</v>
@@ -2756,7 +2756,7 @@
         <v>-0.1948</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5685</v>
+        <v>-0.589</v>
       </c>
       <c r="E51" t="n">
         <v>-0.3643</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.4048</v>
+        <v>-0.4107</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2164</v>
+        <v>-0.2196</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5849</v>
+        <v>-0.6075</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.4048</v>
+        <v>-0.4107</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5285</v>
+        <v>0.5226</v>
       </c>
       <c r="G52" t="n">
         <v>-0.9333</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5285</v>
+        <v>0.5226</v>
       </c>
       <c r="I52" t="n">
         <v>0.5359</v>
@@ -2848,7 +2848,7 @@
         <v>-0.264</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6208</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="E53" t="n">
         <v>-0.4938</v>
@@ -2894,7 +2894,7 @@
         <v>-0.2684</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6242</v>
+        <v>-0.6439</v>
       </c>
       <c r="E54" t="n">
         <v>-0.502</v>
@@ -2940,7 +2940,7 @@
         <v>-0.3742</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-0.7227</v>
       </c>
       <c r="E55" t="n">
         <v>-0.6998</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.7259</v>
+        <v>-0.7205</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.3881</v>
+        <v>-0.3853</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7146</v>
+        <v>-0.731</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.7259</v>
+        <v>-0.7205</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.7259</v>
+        <v>-0.7205</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.7259</v>
+        <v>-0.7205</v>
       </c>
       <c r="I56" t="n">
         <v>-0.7327</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.7638</v>
+        <v>-0.7593</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.4084</v>
+        <v>-0.406</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7299</v>
+        <v>-0.7464</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.7638</v>
+        <v>-0.7593</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.1891</v>
+        <v>-1.1846</v>
       </c>
       <c r="G57" t="n">
         <v>0.4253</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.1891</v>
+        <v>-1.1846</v>
       </c>
       <c r="I57" t="n">
         <v>-1.1946</v>
@@ -3078,7 +3078,7 @@
         <v>-0.4181</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7372</v>
+        <v>-0.7554</v>
       </c>
       <c r="E58" t="n">
         <v>-0.7819</v>
@@ -3124,7 +3124,7 @@
         <v>-0.4234</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7413</v>
+        <v>-0.7594</v>
       </c>
       <c r="E59" t="n">
         <v>-0.7919</v>
@@ -3170,7 +3170,7 @@
         <v>-0.4246</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7421</v>
+        <v>-0.7602</v>
       </c>
       <c r="E60" t="n">
         <v>-0.794</v>
@@ -3216,7 +3216,7 @@
         <v>-0.469</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.7934</v>
       </c>
       <c r="E61" t="n">
         <v>-0.8772</v>
@@ -3262,7 +3262,7 @@
         <v>-0.5052</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.803</v>
+        <v>-0.8203</v>
       </c>
       <c r="E62" t="n">
         <v>-0.9448</v>
@@ -3308,7 +3308,7 @@
         <v>-0.5105</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.8243</v>
       </c>
       <c r="E63" t="n">
         <v>-0.9547</v>
@@ -3354,7 +3354,7 @@
         <v>-0.5479000000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8353</v>
+        <v>-0.8521</v>
       </c>
       <c r="E64" t="n">
         <v>-1.0246</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5561</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8415</v>
+        <v>-0.8583</v>
       </c>
       <c r="E65" t="n">
         <v>-1.0401</v>
@@ -3436,277 +3436,277 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.249</v>
+        <v>-1.2079</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.6459</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.9251</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.249</v>
+        <v>-1.2079</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.249</v>
+        <v>-1.2079</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.249</v>
+        <v>-1.2079</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.249</v>
+        <v>-1.2079</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.249</v>
+        <v>-1.2079</v>
       </c>
       <c r="N66" t="n">
-        <v>59</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.2531</v>
+        <v>-1.249</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.67</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9276</v>
+        <v>-0.9415</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.2531</v>
+        <v>-1.249</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.2531</v>
+        <v>-1.249</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.2531</v>
+        <v>-1.249</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.2531</v>
+        <v>-1.249</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-1.2531</v>
+        <v>-1.249</v>
       </c>
       <c r="N67" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.2644</v>
+        <v>-1.2531</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.6761</v>
+        <v>-0.67</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9322</v>
+        <v>-0.9431</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.2644</v>
+        <v>-1.2531</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.2644</v>
+        <v>-1.2531</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.2644</v>
+        <v>-1.2531</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.2644</v>
+        <v>-1.2531</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.2644</v>
+        <v>-1.2531</v>
       </c>
       <c r="N68" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.2648</v>
+        <v>-1.2644</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.6763</v>
+        <v>-0.6761</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9323</v>
+        <v>-0.9476</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.2648</v>
+        <v>-1.2644</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.2648</v>
+        <v>-1.2644</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.2648</v>
+        <v>-1.2644</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.2648</v>
+        <v>-1.2644</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.2648</v>
+        <v>-1.2644</v>
       </c>
       <c r="N69" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ImpressioN</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.2821</v>
+        <v>-1.2648</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.6855</v>
+        <v>-0.6763</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9393</v>
+        <v>-0.9478</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2821</v>
+        <v>-1.2648</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.2821</v>
+        <v>-1.2648</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.2821</v>
+        <v>-1.2648</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2821</v>
+        <v>-1.2648</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.2821</v>
+        <v>-1.2648</v>
       </c>
       <c r="N70" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>ImpressioN</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.2863</v>
+        <v>-1.2821</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.6878</v>
+        <v>-0.6855</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.9547</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.2863</v>
+        <v>-1.2821</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.2863</v>
+        <v>-1.2821</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.2863</v>
+        <v>-1.2821</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2863</v>
+        <v>-1.2821</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.2863</v>
+        <v>-1.2821</v>
       </c>
       <c r="N71" t="n">
-        <v>122</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72">
@@ -3722,7 +3722,7 @@
         <v>-0.7008</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9508</v>
+        <v>-0.9661</v>
       </c>
       <c r="E72" t="n">
         <v>-1.3106</v>
@@ -3758,231 +3758,231 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.3392</v>
+        <v>-1.3377</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.7161</v>
+        <v>-0.7153</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9624</v>
+        <v>-0.9769</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.3392</v>
+        <v>-1.3377</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.3392</v>
+        <v>-0.49</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>-0.8477</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.3392</v>
+        <v>-0.49</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.3392</v>
+        <v>-0.49</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>-0.8477</v>
       </c>
       <c r="K73" t="n">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.3392</v>
+        <v>-1.3377</v>
       </c>
       <c r="N73" t="n">
-        <v>175</v>
+        <v>219</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.4593</v>
+        <v>-1.3392</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.7803</v>
+        <v>-0.7161</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0109</v>
+        <v>-0.9774</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.4593</v>
+        <v>-1.3392</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.0369</v>
+        <v>-1.3392</v>
       </c>
       <c r="G74" t="n">
-        <v>-1.4224</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.0369</v>
+        <v>-1.3392</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0374</v>
+        <v>-1.3392</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.4224</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="L74" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.4598</v>
+        <v>-1.3392</v>
       </c>
       <c r="N74" t="n">
-        <v>451</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.4652</v>
+        <v>-1.4589</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7835</v>
+        <v>-0.7801</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0133</v>
+        <v>-1.0251</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.4652</v>
+        <v>-1.4589</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.4652</v>
+        <v>-0.0365</v>
       </c>
       <c r="G75" t="n">
-        <v>-1</v>
+        <v>-1.4224</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.4652</v>
+        <v>-0.0365</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4674</v>
+        <v>-0.0374</v>
       </c>
       <c r="J75" t="n">
-        <v>-1</v>
+        <v>-1.4224</v>
       </c>
       <c r="K75" t="n">
-        <v>140</v>
+        <v>214</v>
       </c>
       <c r="L75" t="n">
-        <v>54</v>
+        <v>237</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.4674</v>
+        <v>-1.4598</v>
       </c>
       <c r="N75" t="n">
-        <v>194</v>
+        <v>451</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>w1nt3r</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.4895</v>
+        <v>-1.4635</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7964</v>
+        <v>-0.7825</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0231</v>
+        <v>-1.027</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.4895</v>
+        <v>-1.4635</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.4895</v>
+        <v>-0.4635</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.4895</v>
+        <v>-0.4635</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.4895</v>
+        <v>-0.4674</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K76" t="n">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.4895</v>
+        <v>-1.4674</v>
       </c>
       <c r="N76" t="n">
-        <v>72</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>w1nt3r</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.525</v>
+        <v>-1.4895</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.8154</v>
+        <v>-0.7964</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0374</v>
+        <v>-1.0373</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.525</v>
+        <v>-1.4895</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.6773</v>
+        <v>-1.4895</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.8477</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.6773</v>
+        <v>-1.4895</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.6773</v>
+        <v>-1.4895</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.8477</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="L77" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.525</v>
+        <v>-1.4895</v>
       </c>
       <c r="N77" t="n">
-        <v>219</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78">
@@ -3998,7 +3998,7 @@
         <v>-0.944</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1346</v>
+        <v>-1.1473</v>
       </c>
       <c r="E78" t="n">
         <v>-1.7655</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.9633</v>
+        <v>-1.9288</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.0498</v>
+        <v>-1.0313</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2145</v>
+        <v>-1.2123</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.9633</v>
+        <v>-1.9288</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.8869</v>
+        <v>-0.8524</v>
       </c>
       <c r="G79" t="n">
         <v>-1.0764</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.8869</v>
+        <v>-0.8524</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.8952</v>
+        <v>-0.8668</v>
       </c>
       <c r="J79" t="n">
         <v>-1.0764</v>
@@ -4071,7 +4071,7 @@
         <v>243</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.9716</v>
+        <v>-1.9432</v>
       </c>
       <c r="N79" t="n">
         <v>497</v>
@@ -4090,7 +4090,7 @@
         <v>-1.3646</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4523</v>
+        <v>-1.4606</v>
       </c>
       <c r="E80" t="n">
         <v>-2.552</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.587</v>
+        <v>-2.581</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.3833</v>
+        <v>-1.3801</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.4665</v>
+        <v>-1.4722</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.587</v>
+        <v>-2.581</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.606</v>
+        <v>-1.6</v>
       </c>
       <c r="G81" t="n">
         <v>-0.981</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.606</v>
+        <v>-1.6</v>
       </c>
       <c r="I81" t="n">
         <v>-1.6135</v>
